--- a/santiago 02-09-26.xlsx
+++ b/santiago 02-09-26.xlsx
@@ -1538,7 +1538,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2310,13 +2310,15 @@
       <c r="P21" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="R21" s="46"/>
+      <c r="R21" s="46">
+        <v>1</v>
+      </c>
       <c r="S21" s="47">
-        <v>1275345</v>
+        <v>1235000</v>
       </c>
       <c r="T21" s="48">
         <f>+R21*S21</f>
-        <v>0</v>
+        <v>1235000</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -2387,9 +2389,15 @@
         <f t="shared" ref="P23" si="8">+N23*O23</f>
         <v>1000000</v>
       </c>
-      <c r="R23" s="58"/>
-      <c r="S23" s="59"/>
-      <c r="T23" s="60"/>
+      <c r="R23" s="58">
+        <v>1</v>
+      </c>
+      <c r="S23" s="59">
+        <v>1000000</v>
+      </c>
+      <c r="T23" s="59">
+        <v>1000000</v>
+      </c>
     </row>
     <row r="24" spans="1:22" ht="29">
       <c r="A24" s="49" t="s">
@@ -2589,16 +2597,15 @@
         <v>0</v>
       </c>
       <c r="R28" s="58">
-        <f t="shared" ref="R28:R32" si="11">+N28</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28" s="59">
         <f t="shared" si="9"/>
         <v>500000</v>
       </c>
       <c r="T28" s="60">
-        <f t="shared" ref="T28:T30" si="12">+R28*S28</f>
-        <v>0</v>
+        <f t="shared" ref="T28:T30" si="11">+R28*S28</f>
+        <v>500000</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -2632,7 +2639,7 @@
         <v>500000</v>
       </c>
       <c r="R29" s="58">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="R29:R32" si="12">+N29</f>
         <v>1</v>
       </c>
       <c r="S29" s="59">
@@ -2640,7 +2647,7 @@
         <v>500000</v>
       </c>
       <c r="T29" s="60">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>500000</v>
       </c>
     </row>
@@ -2673,16 +2680,15 @@
         <v>0</v>
       </c>
       <c r="R30" s="58">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" s="59">
         <f t="shared" si="9"/>
         <v>300000</v>
       </c>
       <c r="T30" s="60">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>300000</v>
       </c>
       <c r="V30" s="94" t="s">
         <v>47</v>
@@ -2724,7 +2730,7 @@
         <v>1000000</v>
       </c>
       <c r="R31" s="58">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="S31" s="59">
@@ -2767,7 +2773,7 @@
         <v>500000</v>
       </c>
       <c r="R32" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="S32" s="103">
@@ -3681,7 +3687,7 @@
       <c r="S56" s="118"/>
       <c r="T56" s="119">
         <f>SUM(T15:T55)</f>
-        <v>34503930</v>
+        <v>37538930</v>
       </c>
     </row>
     <row r="57" spans="1:22">
@@ -3710,7 +3716,7 @@
       </c>
       <c r="T57" s="122">
         <f>+T56*0.12</f>
-        <v>4140471.5999999996</v>
+        <v>4504671.5999999996</v>
       </c>
     </row>
     <row r="58" spans="1:22">
@@ -3739,7 +3745,7 @@
       </c>
       <c r="T58" s="122">
         <f>+T56*0.03</f>
-        <v>1035117.8999999999</v>
+        <v>1126167.8999999999</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="15" thickBot="1">
@@ -3768,7 +3774,7 @@
       </c>
       <c r="T59" s="122">
         <f>+T56*0.04</f>
-        <v>1380157.2</v>
+        <v>1501557.2</v>
       </c>
     </row>
     <row r="60" spans="1:22" ht="15" thickBot="1">
@@ -3800,7 +3806,7 @@
       </c>
       <c r="T60" s="127">
         <f>+T59*0.19</f>
-        <v>262229.86800000002</v>
+        <v>285295.86800000002</v>
       </c>
     </row>
     <row r="61" spans="1:22" ht="15" thickBot="1">
@@ -3829,11 +3835,11 @@
       </c>
       <c r="T61" s="127">
         <f>SUM(T56:T60)</f>
-        <v>41321906.568000004</v>
+        <v>44956622.568000004</v>
       </c>
       <c r="V61" s="22">
         <f>+T61-V62</f>
-        <v>-20264793.431999996</v>
+        <v>-16630077.431999996</v>
       </c>
     </row>
     <row r="62" spans="1:22" ht="47.25" customHeight="1" thickBot="1">
@@ -3865,7 +3871,7 @@
       </c>
       <c r="T62" s="132">
         <f>+T61/R15</f>
-        <v>1291309.5802500001</v>
+        <v>1404894.4552500001</v>
       </c>
       <c r="V62">
         <v>61586700</v>
